--- a/sources/wbs.xlsx
+++ b/sources/wbs.xlsx
@@ -447,7 +447,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>(no number) KCGM Growth Work Breakdown Structure</t>
+          <t>(no number) Growth Work Breakdown Structure</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Fimiston Processing</t>
+          <t>FIM Processing</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>General Fimiston Site</t>
+          <t>General FIM Site</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>General Fimiston Site - General</t>
+          <t>General FIM Site - General</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Milling &amp; Classification - Fimiston Existing - Area A</t>
+          <t>Milling &amp; Classification - FIM Existing - Area A</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Milling &amp; Classification - Fimiston Existing - Area A - General</t>
+          <t>Milling &amp; Classification - FIM Existing - Area A - General</t>
         </is>
       </c>
     </row>
@@ -5590,7 +5590,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>General Fimiston Site</t>
+          <t>General FIM Site</t>
         </is>
       </c>
     </row>
@@ -5686,7 +5686,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Milling &amp; Classification - Fimiston Existing - Area A</t>
+          <t>Milling &amp; Classification - FIM Existing - Area A</t>
         </is>
       </c>
     </row>
